--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4541,31 +4541,31 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Ningbo Professional</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -4573,31 +4573,31 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Colon</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
@@ -4605,31 +4605,31 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sheff Utd</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -4637,31 +4637,31 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -4669,31 +4669,31 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Tokyo-V</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Kawasaki</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
@@ -4701,31 +4701,31 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Yamagata</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tochigi Uva FC</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -4733,31 +4733,31 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Ningbo Professional</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
@@ -4765,31 +4765,31 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
@@ -4797,31 +4797,31 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
@@ -4829,31 +4829,31 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -4861,31 +4861,31 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
@@ -4893,31 +4893,31 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>76 Igdir Belediyespor</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
@@ -4925,31 +4925,31 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
@@ -4957,31 +4957,31 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
@@ -4989,31 +4989,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
@@ -5021,31 +5021,31 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
@@ -5053,31 +5053,31 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
@@ -5085,31 +5085,31 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>POLAND 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
@@ -5117,31 +5117,31 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
@@ -5149,31 +5149,31 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>PORTUGAL 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
@@ -5181,31 +5181,31 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Celta Vigo B</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
@@ -5213,31 +5213,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -5245,31 +5245,31 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
@@ -5277,31 +5277,31 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5319,21 +5319,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5351,21 +5351,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
@@ -5373,34 +5373,2434 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sportivo Iteno</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>18.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>COPA SUDAMERICANA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ARGENTINA CUP</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>CA Independiente</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>27</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>COPA SUDAMERICANA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Cienciano</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>19</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>JAPAN 1</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Tokyo-V</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Kashiwa</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>25</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Qingdao Youth Island</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Chongqing Tonglianglong</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>20</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Arges Pitesti</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FRANCE 2</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Club 2 de Mayo de Pedro Juan</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>JAPAN 1</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Hiroshima</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>25</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>JAPAN 2</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>FC Imabari</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Omiya</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>34</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>JAPAN 1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Fukuoka</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>18</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>JAPAN 1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kobe</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>FC Tokyo</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>19</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>JAPAN 2</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sapporo</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>19</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>JAPAN 2</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Shonan</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Yamagata</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>20</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>17</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>17</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Club Football Estrela</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>18</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PORTUGAL 2</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon B</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>18</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CZECH 1</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>MAS Taborsko</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>SFC Opava</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>19</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sheff Utd</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Dinamo Bucharest</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>18</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Estudiantes de Merida</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>20</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Everton De Vina</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Tristan Suarez</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Chaco For Ever</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Otelul Galati</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>22</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>24</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ulsan Hyundai Horang-i</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>17</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Nanjing City</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Jiangxi Dingnan United</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>19</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>DENMARK 1</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AC Horsens</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>20</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PORTUGAL 2</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Lusitania Futebol Clube</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>20</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Estoril Praia</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>16</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Otelul Galati</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BELGIUM 1</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Yellow-Red Mechelen</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>FC Hunedoara</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>18</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>19</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>17</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>20</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>18</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>13</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Santos Laguna</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>FC Anyang</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>22</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>12</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ENGLAND 1</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>12</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ITALY 3</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Foggia</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>9</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>FRANCE 2</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ITALY 3</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Foggia</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>DENMARK 1</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Brondby</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>11</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>10</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>29</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SPAIN 2</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Celta Vigo B</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>34</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Lokomotiv Plovdiv</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>28</v>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>COLOMBIA 2</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Leones FC</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>34</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Ostersunds FK</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Amed Sportif Faaliyetler</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>18</v>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CHILE 2</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>76 Igdir Belediyespor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -514,26 +514,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Antwerp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -622,29 +622,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>18.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>Bodrum Belediyesi Bodrumspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kyoto</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -699,27 +699,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GERMANY 2</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nurnberg</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -730,74 +730,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zilina</t>
+          <t>Colon</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MFK Skalica</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -807,17 +807,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -827,40 +827,40 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Deportes Copiapo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -879,69 +879,69 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLOVENIA 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NK Radomlje</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,33 +951,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -987,24 +987,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -1013,43 +1013,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COPA LIBERTADORES</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Sheff Utd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1059,33 +1059,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Kyoto</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1095,141 +1095,141 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>Nurnberg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GERMANY 2</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Tokyo-V</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vasteras SK</t>
+          <t>Kawasaki</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erokspor A.S</t>
+          <t>Yamagata</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>Tochigi Uva FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1239,105 +1239,105 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GERMANY 2</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Zilina</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St Pauli</t>
+          <t>MFK Skalica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NETHERLANDS 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1347,33 +1347,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PORTUGAL 3</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Santarem</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1383,57 +1383,57 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1455,69 +1455,69 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>PORTUGAL 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Accrington</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1527,57 +1527,57 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>SLOVENIA 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>NK Radomlje</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
@@ -1589,43 +1589,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SCOTLAND 4</t>
+          <t>POLAND 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Annan</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1635,24 +1635,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1661,7 +1661,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1671,60 +1671,60 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Celta Vigo B</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1743,33 +1743,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Melgar</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>COPA LIBERTADORES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -1805,34 +1805,34 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sportivo Iteno</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -1841,7 +1841,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1851,33 +1851,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1887,96 +1887,96 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CS Afumati</t>
+          <t>Anderlecht</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>COPA SUDAMERICANA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SCOTLAND 4</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kelty Hearts</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -1985,7 +1985,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -2021,79 +2021,79 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Club 2 de Mayo de Pedro Juan</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2103,33 +2103,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Vasteras SK</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2139,24 +2139,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Erokspor A.S</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2165,7 +2165,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2175,21 +2175,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>St Pauli</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -2201,7 +2201,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2211,96 +2211,96 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>14</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DENMARK 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mito</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>G-Osaka</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -2345,7 +2345,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2355,33 +2355,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>PORTUGAL 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Santarem</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2391,69 +2391,69 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Tokyo-V</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Kashiwa</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2463,33 +2463,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>POLAND 2</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2499,27 +2499,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Okayama</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Oldham</t>
+          <t>Accrington</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2555,7 +2555,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2566,26 +2566,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>East Fife</t>
+          <t>Sapporo</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -2607,27 +2607,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>POLAND 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2674,32 +2674,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2715,27 +2715,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>SCOTLAND 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
         <v>2</v>
-      </c>
-      <c r="H64" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -2751,27 +2751,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tranmere</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2792,64 +2792,64 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G66" t="n">
         <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FC Inter Turku</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Celta Vigo B</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2885,7 +2885,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2895,33 +2895,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Melgar</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
         <v>3</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2931,33 +2931,33 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2967,33 +2967,33 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3003,33 +3003,33 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3039,69 +3039,69 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>CS Afumati</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
         <v>3</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>CS Afumati</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3111,60 +3111,60 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
         <v>3</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>SCOTLAND 4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Kelty Hearts</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
@@ -3209,79 +3209,79 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Everton De Vina</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3317,34 +3317,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KFC Komarno</t>
+          <t>FC Imabari</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunajska Streda</t>
+          <t>Omiya</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>3</v>
@@ -3353,34 +3353,34 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
         <v>2</v>
@@ -3389,7 +3389,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3399,33 +3399,33 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3440,55 +3440,55 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Fujieda Myfc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Iwaki SC</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
@@ -3497,43 +3497,43 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3543,60 +3543,60 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sport Huancayo</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>SOUTH KOREA 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -3641,7 +3641,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3651,63 +3651,63 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Gwangju FC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3754,32 +3754,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>DENMARK 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CS Afumati</t>
+          <t>HB Koge</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -3795,27 +3795,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Jef Utd Chiba</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>FC Machida</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>SOUTH AFRICA 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Fujieda Myfc</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Iwaki SC</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -3862,32 +3862,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 2</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Kobe</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>FC Tokyo</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -3898,26 +3898,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 1</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sheff Wed</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -3934,32 +3934,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Jef Utd Chiba</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Machida</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3970,32 +3970,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SOUTH AFRICA 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4006,26 +4006,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SLOVENIA 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Mito</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NK Maribor</t>
+          <t>G-Osaka</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -4037,223 +4037,223 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FC Cajamarca</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Barcelona (Ecu)</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="G102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>POLAND 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mardin Buyuksehir Belediyespor</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>URUGUAY 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Okayama</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Oldham</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4263,24 +4263,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>SLOVENIA 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>NK Maribor</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
@@ -4289,34 +4289,34 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>East Fife</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -4325,34 +4325,34 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>POLAND 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -4361,43 +4361,43 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MEXICO 2</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Alacranes de Durango</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Universidad Guadalajara</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4407,60 +4407,60 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Concordia Chiajna</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Politehnica Timisoara</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="G112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -4469,7 +4469,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Sheff Utd</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -4505,7 +4505,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4515,24 +4515,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Shonan</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Yamagata</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -4541,140 +4541,156 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>PORTUGAL 2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Sporting Lisbon B</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ningbo Professional</t>
+          <t>Chaves</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Colon</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sheff Utd</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>24</v>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Bodrum Belediyesi Bodrumspor</t>
+          <t>Tranmere</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>22</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4684,88 +4700,100 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Tokyo-V</t>
+          <t>Urawa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kawasaki</t>
+          <t>Hiroshima</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>19</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>ENGLAND 4</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Yamagata</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tochigi Uva FC</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>18</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ningbo Professional</t>
+          <t>FC Inter Turku</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>19</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4775,125 +4803,141 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>PORTUGAL 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Banik Ostrava B</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>Lusitania Futebol Clube</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>19</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>20</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4903,285 +4947,321 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>76 Igdir Belediyespor</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fatih Karagumruk Istanbul</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Deportes Copiapo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BELGIUM 1</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+        <v>16.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Colo Colo</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F129" t="n">
         <v>20</v>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>18</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tristan Suarez</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>POLAND 2</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>25</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>22</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>FC Cajamarca</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>18</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5196,408 +5276,460 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>19</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>32</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>20</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sportivo Iteno</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>COPA SUDAMERICANA</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>KFC Komarno</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Dunajska Streda</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>27</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+        <v>13.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>COPA SUDAMERICANA</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cienciano</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>19</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tokyo-V</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kashiwa</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>25</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Mardin Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5607,61 +5739,69 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Jiangxi Dingnan United</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5671,93 +5811,105 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hiroshima</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>25</v>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5767,157 +5919,177 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>URUGUAY 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>FC Imabari</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Omiya</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>34</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Fukuoka</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>18</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>JAPAN 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Kobe</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>19</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sapporo</t>
+          <t>Sport Huancayo</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>19</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Shonan</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Yamagata</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>20</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5927,61 +6099,69 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 1</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>17</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ENGLAND 3</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sheff Wed</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>17</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5991,157 +6171,177 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Ulsan Hyundai Horang-i</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>18</v>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sporting Lisbon B</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>18</v>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>CHILE 2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>19</v>
-      </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sheff Utd</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
+        <v>16.5</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>18</v>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6151,61 +6351,69 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>BELGIUM 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Yellow-Red Mechelen</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>20</v>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G165" t="n">
+        <v>3</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6215,189 +6423,213 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tristan Suarez</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>22</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>MEXICO 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Alacranes de Durango</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Universidad Guadalajara</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>24</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6407,29 +6639,33 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 1</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ulsan Hyundai Horang-i</t>
+          <t>Concordia Chiajna</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Politehnica Timisoara</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>17</v>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6439,189 +6675,213 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Jiangxi Dingnan United</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>19</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>20</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PORTUGAL 2</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lusitania Futebol Clube</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>20</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Estoril Praia</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>16</v>
-      </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
+        <v>3.95</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BELGIUM 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6631,29 +6891,33 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>18</v>
-      </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6663,85 +6927,93 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>19</v>
-      </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G181" t="n">
+        <v>2</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Ningbo Professional</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
@@ -6749,7 +7021,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6759,21 +7031,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Ningbo Professional</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
@@ -6781,7 +7053,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6791,21 +7063,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
@@ -6813,31 +7085,31 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
@@ -6845,7 +7117,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6855,21 +7127,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
@@ -6877,31 +7149,31 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -6909,31 +7181,31 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>COPA SUDAMERICANA</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -6941,31 +7213,31 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Santos Laguna</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -6973,31 +7245,31 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>FC Anyang</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6989,63 +6989,61 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ningbo Professional</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ningbo Professional</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
@@ -7053,31 +7051,31 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
@@ -7085,31 +7083,31 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
@@ -7117,31 +7115,31 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
@@ -7149,31 +7147,31 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -7181,7 +7179,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7191,21 +7189,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>COPA SUDAMERICANA</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -7213,31 +7211,31 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -7245,31 +7243,31 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
@@ -7277,31 +7275,31 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
@@ -7309,31 +7307,31 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
@@ -7341,31 +7339,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
@@ -7373,7 +7371,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7383,21 +7381,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -7405,7 +7403,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7415,21 +7413,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
@@ -7437,31 +7435,31 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>15.5</v>
+        <v>9.4</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
@@ -7469,31 +7467,31 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
@@ -7501,31 +7499,31 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -7533,7 +7531,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7543,21 +7541,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
@@ -7565,31 +7563,31 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -7597,31 +7595,31 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
@@ -7629,31 +7627,31 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
@@ -7661,31 +7659,31 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -7693,31 +7691,31 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
@@ -7725,31 +7723,31 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -7757,31 +7755,31 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
@@ -7789,31 +7787,31 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -7821,31 +7819,31 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -7853,31 +7851,31 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Celta Vigo B</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
@@ -7885,31 +7883,31 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
@@ -7917,31 +7915,31 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
@@ -7949,7 +7947,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7959,21 +7957,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
@@ -7981,7 +7979,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7991,21 +7989,21 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -8013,7 +8011,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8023,21 +8021,21 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
@@ -8045,7 +8043,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8055,24 +8053,88 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CHILE 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PARAGUAY CUP</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>General Caballero</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>18</v>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>18</v>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7019,95 +7019,91 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Macara</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
+          <t>Entella</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>SCOTLAND 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>34</v>
-      </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
+          <t>Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
@@ -7115,31 +7111,31 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
@@ -7147,7 +7143,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7157,21 +7153,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -7179,31 +7175,31 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -7216,7 +7212,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7226,16 +7222,16 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -7248,26 +7244,26 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
@@ -7290,12 +7286,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -7317,17 +7313,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -7349,21 +7345,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Sol de America</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
@@ -7381,21 +7377,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -7413,17 +7409,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7440,26 +7436,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
@@ -7472,26 +7468,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
@@ -7504,26 +7500,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -7536,7 +7532,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7555,7 +7551,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
@@ -7568,7 +7564,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7578,16 +7574,16 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -7600,26 +7596,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
@@ -7632,26 +7628,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
@@ -7664,26 +7660,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -7696,7 +7692,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7706,16 +7702,16 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
@@ -7728,26 +7724,26 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -7760,7 +7756,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7770,16 +7766,16 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
@@ -7792,26 +7788,26 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Sol de America</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -7824,26 +7820,26 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -7856,26 +7852,26 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
@@ -7888,7 +7884,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7898,16 +7894,16 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
@@ -7920,26 +7916,26 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
@@ -7957,21 +7953,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
@@ -7989,17 +7985,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -8026,12 +8022,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -8058,16 +8054,16 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
@@ -8085,21 +8081,21 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>General Caballero</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
@@ -8117,24 +8113,152 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ENGLAND CUP</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ENGLAND CUP</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>18</v>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PARAGUAY CUP</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>General Caballero</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Rubio Nu</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>18</v>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>18</v>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7079,95 +7079,103 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>COPA LIBERTADORES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>10.5</v>
+        <v>11.55</v>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
@@ -7175,31 +7183,31 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>EUROPA CHAMPIONS LEAGUE</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>34</v>
+        <v>12.6</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -7207,31 +7215,31 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -7239,31 +7247,31 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>12</v>
+        <v>6.18</v>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
@@ -7271,31 +7279,31 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>COPA SUDAMERICANA</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>11</v>
+        <v>11.55</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
@@ -7303,31 +7311,31 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>COPA SUDAMERICANA</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>10</v>
+        <v>5.05</v>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
@@ -7335,31 +7343,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>10</v>
+        <v>13.12</v>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
@@ -7367,31 +7375,31 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>EUROPA CONFERENCE LEAGUE</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>9.800000000000001</v>
+        <v>6.39</v>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -7399,31 +7407,31 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>11</v>
+        <v>9.68</v>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
@@ -7431,31 +7439,31 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>10</v>
+        <v>6.39</v>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
@@ -7463,7 +7471,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7473,21 +7481,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Sol de America</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
@@ -7495,31 +7503,31 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>11.5</v>
+        <v>6.18</v>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -7527,31 +7535,31 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
@@ -7559,31 +7567,31 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>CROATIA 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Varazdin</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rudes</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>9.4</v>
+        <v>5.97</v>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -7591,12 +7599,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7606,16 +7614,16 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FC Midland</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
@@ -7623,31 +7631,31 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>BRAZIL 3</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
@@ -7655,31 +7663,31 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>8.6</v>
+        <v>5.77</v>
       </c>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -7687,31 +7695,31 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>10.5</v>
+        <v>5.25</v>
       </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
@@ -7719,31 +7727,31 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -7751,31 +7759,31 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
@@ -7783,31 +7791,31 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -7815,31 +7823,31 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ITALY 3</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -7847,31 +7855,31 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ITALY 3</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>AZ Picerno ASD</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
@@ -7879,31 +7887,31 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
@@ -7911,31 +7919,31 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Sol de America</t>
+          <t>Nurnberg</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
@@ -7943,31 +7951,31 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
@@ -7975,31 +7983,31 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -8007,31 +8015,31 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
@@ -8039,31 +8047,31 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 3</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
@@ -8071,31 +8079,31 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
@@ -8103,31 +8111,31 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
@@ -8135,31 +8143,31 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
@@ -8167,31 +8175,31 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
@@ -8199,31 +8207,31 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>General Caballero</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
@@ -8231,34 +8239,4034 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>BRAZIL 3</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>BRAZIL 3</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>7</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7</v>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>8</v>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>12</v>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>14</v>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>24</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>32</v>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>27</v>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>27</v>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>FRANCE 1</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>FRANCE 1</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>17</v>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Calcio Avellino SSD</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>LR Vicenza Virtus</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>COLOMBIA 2</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Real Santander</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>19</v>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>20</v>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>10</v>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>IRELAND 1</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>15</v>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>POLAND 2</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>PORTUGAL 2</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Benfica B</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>10</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SCOTLAND 1</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>12</v>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ENGLAND 1</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Wigan</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>FRANCE 1</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>14</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SCOTLAND 1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>St Mirren</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>POLAND 2</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>11</v>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>8</v>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>11</v>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Arezzo</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>GREECE 1</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>9</v>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ISRAEL 1</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>9</v>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CZECH 1</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Sparta Prague</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Slavia Prague</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>13</v>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>GREECE 1</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Chaco For Ever</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>11</v>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>URUGUAY 1</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>12</v>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>12</v>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Benevento</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>12</v>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>13</v>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>GERMANY 2</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>St Pauli</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>FRANCE 1</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>PORTUGAL 2</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Felgueiras</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Chaco For Ever</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>URUGUAY 1</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Benevento</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>7</v>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>GERMANY 2</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>St Pauli</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>13</v>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>GERMANY 1</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>13</v>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>13</v>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>CZECH 1</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Plzen</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Slovacko</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>NORWAY 2</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Asane</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>14</v>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Ham-Kam</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Kfum Oslo</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>14</v>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>NORWAY 1</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>12</v>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>CROATIA 1</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Slaven Belupo</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Cherno More</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>8</v>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>12</v>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>DENMARK 1</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>NETHERLANDS 1</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>POLAND 2</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>16</v>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>TURKEY 1</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>15</v>
+      </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ISRAEL 1</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>12</v>
+      </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>UKRAINE 1</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Chernomorets Odesa</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Kryvbas Krivyi Rih</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>34</v>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Jeju Utd</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>27</v>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Dalian Kun City FC</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Nantong Zhiyun F.C</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>27</v>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Wigan</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>34</v>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>UKRAINE 1</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Zorya</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>FC Kharkiv</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>34</v>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>POLAND 2</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>34</v>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Arezzo</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>29</v>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>26</v>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>27</v>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>URUGUAY 1</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>30</v>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>UKRAINE 1</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Chernomorets Odesa</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Kryvbas Krivyi Rih</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>18</v>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Incheon Utd</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 1</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Jeju Utd</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>19</v>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CHINA 1</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Dalian Kun City FC</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Nantong Zhiyun F.C</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>20</v>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>ENGLAND 1</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Wigan</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>20</v>
+      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>FRANCE 1</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SWEDEN 2</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Varbergs BoIS</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>SCOTLAND 1</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>St Mirren</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CD Nacional Funchal</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Club Football Estrela</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>18</v>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>AUSTRIA 1</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Hartberg</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>20</v>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>CZECH 1</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Teplice</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>18</v>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>SPAIN 2</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>19</v>
+      </c>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>UKRAINE 1</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Zorya</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>FC Kharkiv</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>20</v>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>POLAND 2</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>18</v>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>CYPRUS 1</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>A.E.L.</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Anorthosis</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>20</v>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Cesar Vallejo Moquegua</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Alianza Atletico</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>18</v>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ITALY 2</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>20</v>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>URUGUAY 1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>20</v>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>PARAGUAY 1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Athletic Bilbao</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Sport Boys (Per)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>19</v>
+      </c>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>20</v>
+      </c>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M402"/>
+  <dimension ref="A1:M487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16181,26 +16181,26 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>15</v>
+        <v>12.6</v>
       </c>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
@@ -16218,26 +16218,26 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>ACS Fotbal Club Bacau</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>CSM Slatina</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>19</v>
+        <v>2.06</v>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
@@ -16255,26 +16255,26 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Al Bukayriyah</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>18</v>
+        <v>5.77</v>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16302,16 +16302,16 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>7.6</v>
+        <v>7.42</v>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
@@ -16329,26 +16329,26 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>27</v>
+        <v>6.59</v>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -16366,26 +16366,26 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Al-Saqer FC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>26</v>
+        <v>6.39</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -16403,40 +16403,32 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>11</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
-      <c r="I366" t="n">
-        <v>0.09774964838255977</v>
-      </c>
-      <c r="J366" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>SEM_ODD</t>
-        </is>
-      </c>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr"/>
     </row>
@@ -16448,26 +16440,26 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>CYPRUS 1</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Omonia FC Aradippou</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>6.2</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
@@ -16485,26 +16477,26 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>7.8</v>
+        <v>5.87</v>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
@@ -16522,26 +16514,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>8.6</v>
+        <v>10.09</v>
       </c>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
@@ -16559,7 +16551,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16578,7 +16570,7 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>9.199999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
@@ -16596,26 +16588,26 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
@@ -16633,26 +16625,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>9</v>
+        <v>14.18</v>
       </c>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
@@ -16670,26 +16662,26 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>18</v>
+        <v>4.63</v>
       </c>
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
@@ -16707,26 +16699,26 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F374" t="n">
-        <v>11</v>
+        <v>10.09</v>
       </c>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
@@ -16739,31 +16731,31 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>20</v>
+        <v>5.92</v>
       </c>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
@@ -16776,31 +16768,31 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>WOM GERMANY 1</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Union Berlin W</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Bayern Munich W</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>12.5</v>
+        <v>6.39</v>
       </c>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
@@ -16813,31 +16805,31 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>ICELAND 2</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>8.6</v>
+        <v>8.24</v>
       </c>
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
@@ -16850,31 +16842,31 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>20</v>
+        <v>6.18</v>
       </c>
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
@@ -16887,31 +16879,31 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Trefelin</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Caernarfon</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>32</v>
+        <v>5.66</v>
       </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
@@ -16924,31 +16916,31 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Holywell</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>17</v>
+        <v>5.15</v>
       </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
@@ -16961,31 +16953,31 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Cardiff Metropolitan</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>TNS</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>10</v>
+        <v>5.66</v>
       </c>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
@@ -16998,31 +16990,31 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>FC Inter Turku</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>17.5</v>
+        <v>5.15</v>
       </c>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
@@ -17035,31 +17027,31 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Ammanford</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Connahs Q.</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>12.5</v>
+        <v>4.89</v>
       </c>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
@@ -17072,31 +17064,31 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>WOM GERMANY 1</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>1.FC Nurnberg W</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Wolfsburg W</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>11.5</v>
+        <v>5.77</v>
       </c>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
@@ -17109,31 +17101,31 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>NORTHERN IRELAND 2</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Strabane Athletic</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>H&amp;W Welders</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>15.5</v>
+        <v>5.15</v>
       </c>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
@@ -17146,31 +17138,31 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>SLOVAKIA 2</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>MFK Bytca</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Z. Moravce-Vrable</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>15</v>
+        <v>4.64</v>
       </c>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
@@ -17183,31 +17175,31 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>6.2</v>
+        <v>5.15</v>
       </c>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
@@ -17220,31 +17212,31 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>ESTONIA 2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Nomme Kalju U21</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Tartu Welco</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>7.8</v>
+        <v>7.21</v>
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
@@ -17257,76 +17249,68 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Westfalia Rhynern</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>SG Dynamo Dresden</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>6.6</v>
+        <v>8.24</v>
       </c>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
-      <c r="I389" t="n">
-        <v>0.07180020811654526</v>
-      </c>
-      <c r="J389" t="n">
-        <v>0.1515151515151515</v>
-      </c>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>SEM_ODD</t>
-        </is>
-      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>11.5</v>
+        <v>6.7</v>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
@@ -17339,31 +17323,31 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SLOVENIA 2</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Krsko Posavje</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Tabor Sezana</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>18</v>
+        <v>4.74</v>
       </c>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
@@ -17376,31 +17360,31 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Phonix Lubeck</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>12</v>
+        <v>7.72</v>
       </c>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
@@ -17413,31 +17397,31 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>7.6</v>
+        <v>5.41</v>
       </c>
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
@@ -17450,31 +17434,31 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>12.5</v>
+        <v>5.66</v>
       </c>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
@@ -17487,31 +17471,31 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>15</v>
+        <v>5.15</v>
       </c>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
@@ -17524,31 +17508,31 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Altglienicke</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
@@ -17561,31 +17545,31 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Wurzburger Kickers</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>11</v>
+        <v>6.18</v>
       </c>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
@@ -17598,31 +17582,31 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Hallescher</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>17</v>
+        <v>7.21</v>
       </c>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
@@ -17635,31 +17619,31 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Al Ettifaq</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>15</v>
+        <v>5.66</v>
       </c>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
@@ -17672,31 +17656,31 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>14.5</v>
+        <v>4.89</v>
       </c>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
@@ -17709,31 +17693,31 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>27</v>
+        <v>5.41</v>
       </c>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -17746,31 +17730,31 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Kauno Zalgiris (LTU)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Besiktas (TUR)</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>7.2</v>
+        <v>5.15</v>
       </c>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
@@ -17780,6 +17764,3151 @@
       <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr"/>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>EUROPA LEAGUE</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Aarhus (DEN)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Benfica (POR)</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA 2</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Ansan Greeners</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Daegu</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>AUSTRIA 2</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Kapfenberg</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>BW Linz</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>WALES 1</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Holywell</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Caernarfon</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Rio Ave</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Croatian HNL</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NK Istra</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Indian Mizoram Premier League</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>MLS FC</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Aizawl FC</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Academico de Viseu</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>CYPRUS 1</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Karmiotissa Polemidion</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>NETHERLANDS 1</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Cambuur Leeuwarden</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>GREECE 1</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>BOSNIA 1</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Lay Draw</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>UKRAINE 1</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Zorya</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>FC Kharkiv</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>11</v>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>GREECE 1</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>FRANCE 2</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>ENGLAND 1</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>12</v>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>15</v>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>9</v>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>11</v>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ENGLAND 5</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Scunthorpe</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>ENGLAND 5</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>AC Oulu</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>15</v>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>15</v>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>DENMARK 1</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>FC Copenhagen</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>SonderjyskE</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>10</v>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SWEDEN 1</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>SWEDEN 1</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Malmo FF</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>15</v>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SPAIN 1</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>11</v>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Lay 2x0</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ENGLAND 5</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>ENGLAND 1</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Asyut Petroleum</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>National Bank</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>25</v>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>ENGLAND 5</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>27</v>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Dunav Ruse</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>32</v>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Al-Saqer FC</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Al-Akhdoud</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>26</v>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>27</v>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>ROMANIA 2</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ACS Fotbal Club Bacau</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>CSM Slatina</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>19</v>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>BULGARIA 1</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Dunav Ruse</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>17</v>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>FINLAND 1</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>FC Inter Turku</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Al Bukayriyah</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Al-Adalh</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>18</v>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>ROMANIA 1</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>18</v>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>FRANCE 2</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>20</v>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>ITALY 1</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>18</v>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>PORTUGAL 1</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Guimaraes</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>20</v>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>CHILE 1</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>17</v>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Lay 0x0</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Bandirmaspor</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>11</v>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Umraniyespor</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Muglaspor</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>11</v>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Swindon</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Lay 0x1</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Umraniyespor</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Muglaspor</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Gillingham</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Lay 1x0</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>10</v>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Lay 0x2</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Boluspor</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Keciorengucu</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Accrington</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>25</v>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Lay 0x3</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Cheltenham</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>24</v>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Bandirmaspor</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>19</v>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Al Jeel</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Jeddah Club</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>19</v>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Al Orubah</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Al-Zulfi SC</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>20</v>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>TURKEY 2</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Sariyer G.K.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Pendikspor</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>19</v>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Al Najma Club</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Al Jabalain</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>18</v>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>ENGLAND 2</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>18</v>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>ENGLAND 3</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Peterborough</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>18</v>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>ENGLAND 4</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Lay 2x2</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Atletico Grau</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>19</v>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M487"/>
+  <dimension ref="A1:M482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19876,7 +19876,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -19886,21 +19886,21 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F460" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
@@ -19913,7 +19913,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -19923,21 +19923,21 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F461" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
@@ -19950,7 +19950,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -19960,21 +19960,21 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Muglaspor</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
@@ -19987,7 +19987,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -19997,21 +19997,21 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F463" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
@@ -20024,31 +20024,31 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
@@ -20061,31 +20061,31 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>West Brom</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
@@ -20098,31 +20098,31 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F466" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
@@ -20135,31 +20135,31 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>SCOTLAND 1</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Muglaspor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr"/>
@@ -20172,31 +20172,31 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>SCOTLAND 1</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="F468" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr"/>
@@ -20209,31 +20209,31 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="F469" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
@@ -20246,31 +20246,31 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>SCOTLAND 1</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr"/>
@@ -20283,7 +20283,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -20293,21 +20293,21 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
@@ -20320,7 +20320,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -20330,17 +20330,17 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Accrington</t>
+          <t>Van Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Grimsby</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -20357,7 +20357,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -20367,21 +20367,21 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>ENGLAND 4</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
@@ -20394,7 +20394,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -20404,17 +20404,17 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Hajer Club</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Al-Anwar Club</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -20431,7 +20431,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -20441,21 +20441,21 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Al Jeel</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>Hradec Kralove</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr"/>
@@ -20468,7 +20468,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -20478,21 +20478,21 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Al-Zulfi SC</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -20520,16 +20520,16 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Mardin Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr"/>
@@ -20542,7 +20542,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -20552,21 +20552,21 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
@@ -20579,7 +20579,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -20594,16 +20594,16 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Blackburn</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
@@ -20616,7 +20616,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -20626,21 +20626,21 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
@@ -20653,7 +20653,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -20663,21 +20663,21 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
@@ -20690,7 +20690,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -20700,21 +20700,21 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Swansea</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F482" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
@@ -20724,191 +20724,6 @@
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr"/>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>ENGLAND 3</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Bromley</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr">
-        <is>
-          <t>Leyton Orient</t>
-        </is>
-      </c>
-      <c r="F483" t="n">
-        <v>18</v>
-      </c>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
-      <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
-      <c r="L483" t="inlineStr"/>
-      <c r="M483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>ENGLAND 3</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Peterborough</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr">
-        <is>
-          <t>Stevenage</t>
-        </is>
-      </c>
-      <c r="F484" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr"/>
-      <c r="M484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>ENGLAND 4</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Rochdale</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>Shrewsbury</t>
-        </is>
-      </c>
-      <c r="F485" t="n">
-        <v>18</v>
-      </c>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
-      <c r="M485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>ENGLAND 4</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Tranmere</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>Rotherham</t>
-        </is>
-      </c>
-      <c r="F486" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
-      <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
-      <c r="L486" t="inlineStr"/>
-      <c r="M486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>PERU 1</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Atletico Grau</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>Melgar</t>
-        </is>
-      </c>
-      <c r="F487" t="n">
-        <v>19</v>
-      </c>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
-      <c r="K487" t="inlineStr"/>
-      <c r="L487" t="inlineStr"/>
-      <c r="M487" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M482"/>
+  <dimension ref="A1:M480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16176,31 +16176,31 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lay Under 0.5 FT (Fav)</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>12.6</v>
+        <v>5.1</v>
       </c>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
@@ -16213,7 +16213,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -16223,21 +16223,21 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
@@ -16255,26 +16255,26 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>5.77</v>
+        <v>12.6</v>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -16297,21 +16297,21 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>7.42</v>
+        <v>2.06</v>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
@@ -16334,21 +16334,21 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>6.59</v>
+        <v>5.77</v>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -16371,21 +16371,21 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>6.39</v>
+        <v>7.42</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -16408,21 +16408,21 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>8.449999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
@@ -16440,26 +16440,26 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CYPRUS 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Omonia FC Aradippou</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>8.029999999999999</v>
+        <v>6.39</v>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
@@ -16477,26 +16477,26 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>5.87</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
@@ -16514,26 +16514,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>CYPRUS 1</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Omonia FC Aradippou</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>10.09</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
@@ -16551,26 +16551,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>7.21</v>
+        <v>5.87</v>
       </c>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
@@ -16588,26 +16588,26 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>18.5</v>
+        <v>10.09</v>
       </c>
       <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
@@ -16625,26 +16625,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lay Under 0.5 FT (Fav)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>14.18</v>
+        <v>7.21</v>
       </c>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
@@ -16662,26 +16662,26 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>4.63</v>
+        <v>18.5</v>
       </c>
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
+          <t>Lay Under 0.5 FT (Fav)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>10.09</v>
+        <v>14.18</v>
       </c>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
@@ -16731,7 +16731,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -16741,21 +16741,21 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>5.92</v>
+        <v>4.63</v>
       </c>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
@@ -16768,31 +16768,31 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>WOM GERMANY 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Union Berlin W</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Bayern Munich W</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>6.39</v>
+        <v>10.09</v>
       </c>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
@@ -16815,21 +16815,21 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ICELAND 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>8.24</v>
+        <v>5.92</v>
       </c>
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
@@ -16852,21 +16852,21 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>WOM GERMANY 1</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Union Berlin W</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern Munich W</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>6.18</v>
+        <v>6.39</v>
       </c>
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
@@ -16889,21 +16889,21 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>ICELAND 2</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Trefelin</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Caernarfon</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>5.66</v>
+        <v>8.24</v>
       </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
@@ -16926,21 +16926,21 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Holywell</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>5.15</v>
+        <v>6.18</v>
       </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
@@ -16968,12 +16968,12 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Cardiff Metropolitan</t>
+          <t>Trefelin</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Caernarfon</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -16990,7 +16990,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Holywell</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -17027,7 +17027,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -17042,16 +17042,16 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Ammanford</t>
+          <t>Cardiff Metropolitan</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Connahs Q.</t>
+          <t>TNS</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>4.89</v>
+        <v>5.66</v>
       </c>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
@@ -17074,21 +17074,21 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>WOM GERMANY 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>1.FC Nurnberg W</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Wolfsburg W</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>5.77</v>
+        <v>5.15</v>
       </c>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
@@ -17111,21 +17111,21 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>NORTHERN IRELAND 2</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Strabane Athletic</t>
+          <t>Ammanford</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>H&amp;W Welders</t>
+          <t>Connahs Q.</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>5.15</v>
+        <v>4.89</v>
       </c>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
@@ -17148,21 +17148,21 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>SLOVAKIA 2</t>
+          <t>WOM GERMANY 1</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>MFK Bytca</t>
+          <t>1.FC Nurnberg W</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Z. Moravce-Vrable</t>
+          <t>Wolfsburg W</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>4.64</v>
+        <v>5.77</v>
       </c>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
@@ -17185,17 +17185,17 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>NORTHERN IRELAND 2</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Strabane Athletic</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>H&amp;W Welders</t>
         </is>
       </c>
       <c r="F387" t="n">
@@ -17212,7 +17212,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -17222,21 +17222,21 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ESTONIA 2</t>
+          <t>SLOVAKIA 2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Nomme Kalju U21</t>
+          <t>MFK Bytca</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Tartu Welco</t>
+          <t>Z. Moravce-Vrable</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>7.21</v>
+        <v>4.64</v>
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
@@ -17249,7 +17249,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -17259,21 +17259,21 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Westfalia Rhynern</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>SG Dynamo Dresden</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>8.24</v>
+        <v>5.15</v>
       </c>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
@@ -17296,21 +17296,21 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>ESTONIA 2</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nomme Kalju U21</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Tartu Welco</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>6.7</v>
+        <v>7.21</v>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
@@ -17333,21 +17333,21 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>SLOVENIA 2</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Krsko Posavje</t>
+          <t>Westfalia Rhynern</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Tabor Sezana</t>
+          <t>SG Dynamo Dresden</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>4.74</v>
+        <v>8.24</v>
       </c>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
@@ -17370,21 +17370,21 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Phonix Lubeck</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>7.72</v>
+        <v>6.7</v>
       </c>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
@@ -17407,21 +17407,21 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>SLOVENIA 2</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Krsko Posavje</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Tabor Sezana</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>5.41</v>
+        <v>4.74</v>
       </c>
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
@@ -17444,21 +17444,21 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Phonix Lubeck</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>5.66</v>
+        <v>7.72</v>
       </c>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -17481,21 +17481,21 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>5.15</v>
+        <v>5.41</v>
       </c>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
@@ -17508,7 +17508,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -17518,21 +17518,21 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Altglienicke</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>9.27</v>
+        <v>5.66</v>
       </c>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
@@ -17560,16 +17560,16 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
@@ -17597,16 +17597,16 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Altglienicke</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>7.21</v>
+        <v>9.27</v>
       </c>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
@@ -17619,7 +17619,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -17629,21 +17629,21 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Al Ettifaq</t>
+          <t>Wurzburger Kickers</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>5.66</v>
+        <v>6.18</v>
       </c>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
@@ -17656,7 +17656,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -17666,21 +17666,21 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>GERMANY CUP</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Hallescher</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Schalke</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>4.89</v>
+        <v>7.21</v>
       </c>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
@@ -17693,7 +17693,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -17703,21 +17703,21 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Al Ettifaq</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>5.41</v>
+        <v>5.66</v>
       </c>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -17730,7 +17730,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -17740,21 +17740,21 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Kauno Zalgiris (LTU)</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Besiktas (TUR)</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>5.15</v>
+        <v>4.89</v>
       </c>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
@@ -17767,7 +17767,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -17777,21 +17777,21 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Aarhus (DEN)</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Benfica (POR)</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>4.89</v>
+        <v>5.41</v>
       </c>
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
@@ -17804,7 +17804,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -17814,21 +17814,21 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 2</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Kauno Zalgiris (LTU)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Besiktas (TUR)</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>4.64</v>
+        <v>5.15</v>
       </c>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
@@ -17841,7 +17841,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -17851,17 +17851,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>AUSTRIA 2</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Kapfenberg</t>
+          <t>Aarhus (DEN)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>BW Linz</t>
+          <t>Benfica (POR)</t>
         </is>
       </c>
       <c r="F405" t="n">
@@ -17888,17 +17888,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>SOUTH KOREA 2</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F406" t="n">
@@ -17925,21 +17925,21 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>AUSTRIA 2</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Holywell</t>
+          <t>Kapfenberg</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Caernarfon</t>
+          <t>BW Linz</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>6.18</v>
+        <v>4.89</v>
       </c>
       <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
@@ -17962,21 +17962,21 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>5.66</v>
+        <v>4.64</v>
       </c>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
@@ -17989,7 +17989,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -17999,21 +17999,21 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Croatian HNL</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>NK Istra</t>
+          <t>Holywell</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Caernarfon</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>6.08</v>
+        <v>6.18</v>
       </c>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
@@ -18026,7 +18026,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -18036,21 +18036,21 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Indian Mizoram Premier League</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>MLS FC</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Aizawl FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>6.8</v>
+        <v>5.66</v>
       </c>
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
@@ -18073,21 +18073,21 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Croatian HNL</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>NK Istra</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>5.67</v>
+        <v>6.08</v>
       </c>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
@@ -18100,7 +18100,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -18110,21 +18110,21 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>CYPRUS 1</t>
+          <t>Indian Mizoram Premier League</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Karmiotissa Polemidion</t>
+          <t>MLS FC</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Aizawl FC</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>6.18</v>
+        <v>6.8</v>
       </c>
       <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr"/>
@@ -18137,7 +18137,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -18147,21 +18147,21 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>6.59</v>
+        <v>5.67</v>
       </c>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
@@ -18184,21 +18184,21 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>CYPRUS 1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Karmiotissa Polemidion</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>5.77</v>
+        <v>6.18</v>
       </c>
       <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr"/>
@@ -18221,21 +18221,21 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>5.46</v>
+        <v>6.59</v>
       </c>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
@@ -18248,7 +18248,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -18258,21 +18258,21 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>5.25</v>
+        <v>5.77</v>
       </c>
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
@@ -18285,31 +18285,31 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>6.6</v>
+        <v>5.46</v>
       </c>
       <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
@@ -18322,31 +18322,31 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>FC Kharkiv</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>11</v>
+        <v>5.25</v>
       </c>
       <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
@@ -18364,26 +18364,26 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr"/>
@@ -18401,26 +18401,26 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr"/>
@@ -18443,21 +18443,21 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr"/>
@@ -18480,21 +18480,21 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr"/>
@@ -18517,21 +18517,21 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr"/>
@@ -18554,21 +18554,21 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr"/>
@@ -18586,26 +18586,26 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr"/>
@@ -18623,26 +18623,26 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
@@ -18665,21 +18665,21 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr"/>
@@ -18702,21 +18702,21 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
@@ -18739,21 +18739,21 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
@@ -18776,21 +18776,21 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
@@ -18808,26 +18808,26 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr"/>
@@ -18845,26 +18845,26 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr"/>
@@ -18887,21 +18887,21 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr"/>
@@ -18924,21 +18924,21 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr"/>
@@ -18966,12 +18966,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -18998,21 +18998,21 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr"/>
@@ -19035,21 +19035,21 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
@@ -19072,21 +19072,21 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>DENMARK 1</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>SonderjyskE</t>
         </is>
       </c>
       <c r="F438" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
@@ -19109,17 +19109,17 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F439" t="n">
@@ -19146,21 +19146,21 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="F440" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
@@ -19188,16 +19188,16 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F441" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
@@ -19220,21 +19220,21 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
@@ -19257,21 +19257,21 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F443" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
@@ -19289,26 +19289,26 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F444" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
@@ -19326,26 +19326,26 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F445" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
@@ -19363,26 +19363,26 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
@@ -19400,26 +19400,26 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
@@ -19442,21 +19442,21 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
@@ -19479,21 +19479,21 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Al-Saqer FC</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
@@ -19516,21 +19516,21 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
@@ -19548,26 +19548,26 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>ACS Fotbal Club Bacau</t>
+          <t>Al-Saqer FC</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>CSM Slatina</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
@@ -19585,26 +19585,26 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
@@ -19627,21 +19627,21 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>FC Inter Turku</t>
+          <t>ACS Fotbal Club Bacau</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>CSM Slatina</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
@@ -19664,21 +19664,21 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Al Bukayriyah</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
@@ -19701,21 +19701,21 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>FC Inter Turku</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
@@ -19738,21 +19738,21 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Bukayriyah</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
@@ -19775,17 +19775,17 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -19812,17 +19812,17 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -19849,21 +19849,21 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>CHILE 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr"/>
@@ -19876,31 +19876,31 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="F460" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
@@ -19913,31 +19913,31 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>CHILE 1</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F461" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="F462" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
@@ -19997,21 +19997,21 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F463" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
@@ -20029,26 +20029,26 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
@@ -20066,26 +20066,26 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>West Brom</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Charlton</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
@@ -20103,26 +20103,26 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>ENGLAND 3</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F466" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
@@ -20140,26 +20140,26 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr"/>
@@ -20172,31 +20172,31 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Dundee Utd</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F468" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr"/>
@@ -20209,31 +20209,31 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>ENGLAND 3</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F469" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
@@ -20246,31 +20246,31 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr"/>
@@ -20283,31 +20283,31 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>SWITZERLAND 1</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
@@ -20320,31 +20320,31 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Van Buyuksehir Belediyespor</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr"/>
@@ -20357,7 +20357,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -20367,21 +20367,21 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
@@ -20394,31 +20394,31 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Hajer Club</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Al-Anwar Club</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr"/>
@@ -20431,7 +20431,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -20441,21 +20441,21 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>76 Igdir Belediyespor</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Hradec Kralove</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr"/>
@@ -20468,7 +20468,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -20478,21 +20478,21 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Fatih Karagumruk Istanbul</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr"/>
@@ -20505,7 +20505,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -20515,21 +20515,21 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Mardin Buyuksehir Belediyespor</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr"/>
@@ -20542,7 +20542,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -20552,17 +20552,17 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -20579,7 +20579,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -20589,21 +20589,21 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
@@ -20616,7 +20616,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -20626,21 +20626,21 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>ENGLAND 3</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
@@ -20650,80 +20650,6 @@
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr"/>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>PARAGUAY 1</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Club Sportivo Ameliano</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>Sportivo Trinidense</t>
-        </is>
-      </c>
-      <c r="F481" t="n">
-        <v>18</v>
-      </c>
-      <c r="G481" t="inlineStr"/>
-      <c r="H481" t="inlineStr"/>
-      <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
-      <c r="M481" t="inlineStr"/>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>COLOMBIA 1</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="F482" t="n">
-        <v>20</v>
-      </c>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
-      <c r="M482" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M480"/>
+  <dimension ref="A1:M409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16176,31 +16176,31 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
@@ -16213,31 +16213,31 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
@@ -16250,31 +16250,31 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Lay Under 0.5 FT (Fav)</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -16287,31 +16287,31 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>FC Kharkiv</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>2.06</v>
+        <v>16</v>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
@@ -16324,31 +16324,31 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>ARGENTINA CUP</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>5.77</v>
+        <v>32</v>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -16361,31 +16361,31 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>7.42</v>
+        <v>20</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -16398,31 +16398,31 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>6.59</v>
+        <v>11</v>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
@@ -16435,31 +16435,31 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>6.39</v>
+        <v>9.4</v>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
@@ -16472,31 +16472,31 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>8.449999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
@@ -16509,31 +16509,31 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>CYPRUS 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Omonia FC Aradippou</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>8.029999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
@@ -16546,31 +16546,31 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>5.87</v>
+        <v>7.8</v>
       </c>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
@@ -16583,31 +16583,31 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>DENMARK 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>SonderjyskE</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>10.09</v>
+        <v>28</v>
       </c>
       <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
@@ -16620,31 +16620,31 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>7.21</v>
+        <v>17</v>
       </c>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
@@ -16657,31 +16657,31 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
@@ -16694,31 +16694,31 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Lay Under 0.5 FT (Fav)</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F374" t="n">
-        <v>14.18</v>
+        <v>19</v>
       </c>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
@@ -16731,31 +16731,31 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>4.63</v>
+        <v>19.5</v>
       </c>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
@@ -16768,31 +16768,31 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lay Away / DC 1X (Fav &lt;= 1.45)</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>10.09</v>
+        <v>7.4</v>
       </c>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
@@ -16805,31 +16805,31 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>5.92</v>
+        <v>19.5</v>
       </c>
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
@@ -16842,31 +16842,31 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>WOM GERMANY 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Union Berlin W</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Bayern Munich W</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>6.39</v>
+        <v>7.2</v>
       </c>
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
@@ -16879,31 +16879,31 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>ICELAND 2</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>8.24</v>
+        <v>14</v>
       </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
@@ -16916,31 +16916,31 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>6.18</v>
+        <v>13</v>
       </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
@@ -16953,31 +16953,31 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Trefelin</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Caernarfon</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>5.66</v>
+        <v>13</v>
       </c>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
@@ -16990,31 +16990,31 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Holywell</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
@@ -17027,31 +17027,31 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Cardiff Metropolitan</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>5.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
@@ -17064,31 +17064,31 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>5.15</v>
+        <v>11.5</v>
       </c>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
@@ -17101,31 +17101,31 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Ammanford</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Connahs Q.</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>4.89</v>
+        <v>11</v>
       </c>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
@@ -17138,31 +17138,31 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>WOM GERMANY 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>1.FC Nurnberg W</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Wolfsburg W</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>5.77</v>
+        <v>9.4</v>
       </c>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
@@ -17175,31 +17175,31 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>NORTHERN IRELAND 2</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Strabane Athletic</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>H&amp;W Welders</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>5.15</v>
+        <v>11</v>
       </c>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
@@ -17212,31 +17212,31 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SLOVAKIA 2</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>MFK Bytca</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Z. Moravce-Vrable</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>4.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
@@ -17249,31 +17249,31 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>5.15</v>
+        <v>12.5</v>
       </c>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
@@ -17286,31 +17286,31 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ESTONIA 2</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Nomme Kalju U21</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Tartu Welco</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>7.21</v>
+        <v>6.8</v>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
@@ -17323,31 +17323,31 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Westfalia Rhynern</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>SG Dynamo Dresden</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>8.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
@@ -17360,31 +17360,31 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
@@ -17397,31 +17397,31 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SLOVENIA 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Krsko Posavje</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Tabor Sezana</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>4.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
@@ -17434,31 +17434,31 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Phonix Lubeck</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>7.72</v>
+        <v>9.4</v>
       </c>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
@@ -17471,31 +17471,31 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>5.41</v>
+        <v>9</v>
       </c>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
@@ -17508,12 +17508,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17523,16 +17523,16 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>5.66</v>
+        <v>14</v>
       </c>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
@@ -17545,31 +17545,31 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>5.15</v>
+        <v>13.5</v>
       </c>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
@@ -17582,31 +17582,31 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Altglienicke</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>9.27</v>
+        <v>11</v>
       </c>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
@@ -17619,31 +17619,31 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>6.18</v>
+        <v>10.5</v>
       </c>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
@@ -17656,31 +17656,31 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>GERMANY CUP</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>7.21</v>
+        <v>32</v>
       </c>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
@@ -17693,31 +17693,31 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Al Ettifaq</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>5.66</v>
+        <v>30</v>
       </c>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -17730,31 +17730,31 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Al-Saqer FC</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>4.89</v>
+        <v>18</v>
       </c>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
@@ -17767,31 +17767,31 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Al-Wahda (KSA)</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>5.41</v>
+        <v>18</v>
       </c>
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
@@ -17804,31 +17804,31 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Kauno Zalgiris (LTU)</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Besiktas (TUR)</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>5.15</v>
+        <v>19.5</v>
       </c>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
@@ -17841,31 +17841,31 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Aarhus (DEN)</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Benfica (POR)</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>4.89</v>
+        <v>20</v>
       </c>
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
@@ -17878,31 +17878,31 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>4.64</v>
+        <v>19</v>
       </c>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
@@ -17915,31 +17915,31 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>AUSTRIA 2</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Kapfenberg</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>BW Linz</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>4.89</v>
+        <v>19.5</v>
       </c>
       <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
@@ -17952,31 +17952,31 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>4.64</v>
+        <v>20</v>
       </c>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
@@ -17989,31 +17989,31 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Holywell</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Caernarfon</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>6.18</v>
+        <v>20</v>
       </c>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
@@ -18023,2633 +18023,6 @@
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr"/>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>PORTUGAL 1</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>Rio Ave</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>Sporting CP</t>
-        </is>
-      </c>
-      <c r="F410" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="G410" t="inlineStr"/>
-      <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
-      <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
-      <c r="L410" t="inlineStr"/>
-      <c r="M410" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>Croatian HNL</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>NK Istra</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb</t>
-        </is>
-      </c>
-      <c r="F411" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="G411" t="inlineStr"/>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
-      <c r="M411" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>Indian Mizoram Premier League</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>MLS FC</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>Aizawl FC</t>
-        </is>
-      </c>
-      <c r="F412" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
-      <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>Portuguese Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>Academico de Viseu</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="F413" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G413" t="inlineStr"/>
-      <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>CYPRUS 1</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>Karmiotissa Polemidion</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>Pafos FC</t>
-        </is>
-      </c>
-      <c r="F414" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>NETHERLANDS 1</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>Cambuur Leeuwarden</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>FC Twente</t>
-        </is>
-      </c>
-      <c r="F415" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>GREECE 1</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>Kifisia</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>AEK Athens</t>
-        </is>
-      </c>
-      <c r="F416" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr"/>
-      <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
-      <c r="L416" t="inlineStr"/>
-      <c r="M416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>BOSNIA 1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>Radnik Bijeljina</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>Borac Banja Luka</t>
-        </is>
-      </c>
-      <c r="F417" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
-      <c r="L417" t="inlineStr"/>
-      <c r="M417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Lay Draw</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>UKRAINE 1</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>Zorya</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>FC Kharkiv</t>
-        </is>
-      </c>
-      <c r="F418" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
-      <c r="M418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Lay 0x0</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>SPAIN 1</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="F419" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
-      <c r="M419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Lay 0x0</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>Arda</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>Botev Vratsa</t>
-        </is>
-      </c>
-      <c r="F420" t="n">
-        <v>11</v>
-      </c>
-      <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
-      <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
-      <c r="M420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>GREECE 1</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>Levadiakos</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>Panathinaikos</t>
-        </is>
-      </c>
-      <c r="F421" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
-      <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr"/>
-      <c r="L421" t="inlineStr"/>
-      <c r="M421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>EGYPT 1</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>Al-Masry</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>Pyramids</t>
-        </is>
-      </c>
-      <c r="F422" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr"/>
-      <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
-      <c r="M422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>Dijon</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="F423" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
-      <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr"/>
-      <c r="L423" t="inlineStr"/>
-      <c r="M423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>ENGLAND 1</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="F424" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
-      <c r="M424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>BRAZIL 1</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F425" t="n">
-        <v>12</v>
-      </c>
-      <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
-      <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr"/>
-      <c r="L425" t="inlineStr"/>
-      <c r="M425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>ARGENTINA 1</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>Instituto</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>San Lorenzo</t>
-        </is>
-      </c>
-      <c r="F426" t="n">
-        <v>15</v>
-      </c>
-      <c r="G426" t="inlineStr"/>
-      <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
-      <c r="M426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>EGYPT 1</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>Zamalek</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>Petrojet</t>
-        </is>
-      </c>
-      <c r="F427" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
-      <c r="M427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>Arda</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>Botev Vratsa</t>
-        </is>
-      </c>
-      <c r="F428" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
-      <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr"/>
-      <c r="L428" t="inlineStr"/>
-      <c r="M428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="F429" t="n">
-        <v>9</v>
-      </c>
-      <c r="G429" t="inlineStr"/>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
-      <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr"/>
-      <c r="L429" t="inlineStr"/>
-      <c r="M429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>CHILE 1</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="F430" t="n">
-        <v>11</v>
-      </c>
-      <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr"/>
-      <c r="I430" t="inlineStr"/>
-      <c r="J430" t="inlineStr"/>
-      <c r="K430" t="inlineStr"/>
-      <c r="L430" t="inlineStr"/>
-      <c r="M430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>BRAZIL 1</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F431" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
-      <c r="M431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>ARGENTINA 1</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>Instituto</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>San Lorenzo</t>
-        </is>
-      </c>
-      <c r="F432" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G432" t="inlineStr"/>
-      <c r="H432" t="inlineStr"/>
-      <c r="I432" t="inlineStr"/>
-      <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
-      <c r="M432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>ENGLAND 5</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>Carlisle</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>Scunthorpe</t>
-        </is>
-      </c>
-      <c r="F433" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G433" t="inlineStr"/>
-      <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
-      <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
-      <c r="M433" t="inlineStr"/>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>ENGLAND 5</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>Forest Green</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>Altrincham</t>
-        </is>
-      </c>
-      <c r="F434" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G434" t="inlineStr"/>
-      <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
-      <c r="J434" t="inlineStr"/>
-      <c r="K434" t="inlineStr"/>
-      <c r="L434" t="inlineStr"/>
-      <c r="M434" t="inlineStr"/>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>AC Oulu</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>SJK</t>
-        </is>
-      </c>
-      <c r="F435" t="n">
-        <v>15</v>
-      </c>
-      <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr"/>
-      <c r="J435" t="inlineStr"/>
-      <c r="K435" t="inlineStr"/>
-      <c r="L435" t="inlineStr"/>
-      <c r="M435" t="inlineStr"/>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>Gnistan</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>TPS</t>
-        </is>
-      </c>
-      <c r="F436" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G436" t="inlineStr"/>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
-      <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
-      <c r="M436" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>VPS</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>Lahti</t>
-        </is>
-      </c>
-      <c r="F437" t="n">
-        <v>15</v>
-      </c>
-      <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
-      <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr"/>
-      <c r="L437" t="inlineStr"/>
-      <c r="M437" t="inlineStr"/>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>DENMARK 1</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>FC Copenhagen</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>SonderjyskE</t>
-        </is>
-      </c>
-      <c r="F438" t="n">
-        <v>10</v>
-      </c>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
-      <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>SWEDEN 1</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>GAIS</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>Brommapojkarna</t>
-        </is>
-      </c>
-      <c r="F439" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
-      <c r="K439" t="inlineStr"/>
-      <c r="L439" t="inlineStr"/>
-      <c r="M439" t="inlineStr"/>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>SWEDEN 1</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>Sirius</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>Malmo FF</t>
-        </is>
-      </c>
-      <c r="F440" t="n">
-        <v>15</v>
-      </c>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
-      <c r="M440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>SPAIN 1</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="F441" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr"/>
-      <c r="M441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>Arda</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>Botev Vratsa</t>
-        </is>
-      </c>
-      <c r="F442" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
-      <c r="M442" t="inlineStr"/>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>SPAIN 1</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="F443" t="n">
-        <v>11</v>
-      </c>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr"/>
-      <c r="L443" t="inlineStr"/>
-      <c r="M443" t="inlineStr"/>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>BRAZIL 1</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F444" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" t="inlineStr"/>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>ARGENTINA 1</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>Tigre</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="F445" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr"/>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Lay 0x2</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>ENGLAND 5</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>Woking</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>Southend</t>
-        </is>
-      </c>
-      <c r="F446" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G446" t="inlineStr"/>
-      <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr"/>
-      <c r="L446" t="inlineStr"/>
-      <c r="M446" t="inlineStr"/>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Lay 0x2</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>ENGLAND 1</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="F447" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr"/>
-      <c r="M447" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>EGYPT 1</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>Asyut Petroleum</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>National Bank</t>
-        </is>
-      </c>
-      <c r="F448" t="n">
-        <v>25</v>
-      </c>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>ENGLAND 5</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>Woking</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>Southend</t>
-        </is>
-      </c>
-      <c r="F449" t="n">
-        <v>27</v>
-      </c>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
-      <c r="M449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>Dunav Ruse</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia</t>
-        </is>
-      </c>
-      <c r="F450" t="n">
-        <v>32</v>
-      </c>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>Al-Saqer FC</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>Al-Akhdoud</t>
-        </is>
-      </c>
-      <c r="F451" t="n">
-        <v>26</v>
-      </c>
-      <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr"/>
-      <c r="L451" t="inlineStr"/>
-      <c r="M451" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>EGYPT 1</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>Al-Masry</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>Pyramids</t>
-        </is>
-      </c>
-      <c r="F452" t="n">
-        <v>27</v>
-      </c>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr"/>
-      <c r="M452" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>ROMANIA 2</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>ACS Fotbal Club Bacau</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>CSM Slatina</t>
-        </is>
-      </c>
-      <c r="F453" t="n">
-        <v>19</v>
-      </c>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
-      <c r="J453" t="inlineStr"/>
-      <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr"/>
-      <c r="M453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>BULGARIA 1</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>Dunav Ruse</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia</t>
-        </is>
-      </c>
-      <c r="F454" t="n">
-        <v>17</v>
-      </c>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
-      <c r="M454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>FC Inter Turku</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>KuPS</t>
-        </is>
-      </c>
-      <c r="F455" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
-      <c r="M455" t="inlineStr"/>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>Al Bukayriyah</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>Al-Adalh</t>
-        </is>
-      </c>
-      <c r="F456" t="n">
-        <v>18</v>
-      </c>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
-      <c r="K456" t="inlineStr"/>
-      <c r="L456" t="inlineStr"/>
-      <c r="M456" t="inlineStr"/>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>ROMANIA 1</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>Rapid Bucharest</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>Universitatea Craiova</t>
-        </is>
-      </c>
-      <c r="F457" t="n">
-        <v>18</v>
-      </c>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
-      <c r="K457" t="inlineStr"/>
-      <c r="L457" t="inlineStr"/>
-      <c r="M457" t="inlineStr"/>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>Dijon</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="F458" t="n">
-        <v>20</v>
-      </c>
-      <c r="G458" t="inlineStr"/>
-      <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
-      <c r="K458" t="inlineStr"/>
-      <c r="L458" t="inlineStr"/>
-      <c r="M458" t="inlineStr"/>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="F459" t="n">
-        <v>18</v>
-      </c>
-      <c r="G459" t="inlineStr"/>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
-      <c r="M459" t="inlineStr"/>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>PORTUGAL 1</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Braga</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>Guimaraes</t>
-        </is>
-      </c>
-      <c r="F460" t="n">
-        <v>20</v>
-      </c>
-      <c r="G460" t="inlineStr"/>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
-      <c r="M460" t="inlineStr"/>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>CHILE 1</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Union La Calera</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="F461" t="n">
-        <v>17</v>
-      </c>
-      <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
-      <c r="L461" t="inlineStr"/>
-      <c r="M461" t="inlineStr"/>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Lay 0x0</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>ARGENTINA CUP</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Velez Sarsfield</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="F462" t="n">
-        <v>10</v>
-      </c>
-      <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
-      <c r="K462" t="inlineStr"/>
-      <c r="L462" t="inlineStr"/>
-      <c r="M462" t="inlineStr"/>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>ARGENTINA CUP</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>Velez Sarsfield</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="F463" t="n">
-        <v>8</v>
-      </c>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
-      <c r="M463" t="inlineStr"/>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>COLOMBIA 1</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="F464" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr"/>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="inlineStr"/>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Lay 0x2</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>COLOMBIA 1</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="F465" t="n">
-        <v>16</v>
-      </c>
-      <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
-      <c r="K465" t="inlineStr"/>
-      <c r="L465" t="inlineStr"/>
-      <c r="M465" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>ARGENTINA CUP</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>Velez Sarsfield</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="F466" t="n">
-        <v>32</v>
-      </c>
-      <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr"/>
-      <c r="L466" t="inlineStr"/>
-      <c r="M466" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>COLOMBIA 1</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="F467" t="n">
-        <v>20</v>
-      </c>
-      <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr"/>
-      <c r="I467" t="inlineStr"/>
-      <c r="J467" t="inlineStr"/>
-      <c r="K467" t="inlineStr"/>
-      <c r="L467" t="inlineStr"/>
-      <c r="M467" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>FRANCE 1</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="F468" t="n">
-        <v>9</v>
-      </c>
-      <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
-      <c r="K468" t="inlineStr"/>
-      <c r="L468" t="inlineStr"/>
-      <c r="M468" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Lay 0x1</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>ECUADOR 1</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="E469" t="inlineStr">
-        <is>
-          <t>Emelec</t>
-        </is>
-      </c>
-      <c r="F469" t="n">
-        <v>11</v>
-      </c>
-      <c r="G469" t="inlineStr"/>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
-      <c r="K469" t="inlineStr"/>
-      <c r="L469" t="inlineStr"/>
-      <c r="M469" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Lay 1x0</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>ECUADOR 1</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr">
-        <is>
-          <t>Emelec</t>
-        </is>
-      </c>
-      <c r="F470" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G470" t="inlineStr"/>
-      <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr"/>
-      <c r="J470" t="inlineStr"/>
-      <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
-      <c r="M470" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>SWITZERLAND 1</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>Lugano</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>Servette</t>
-        </is>
-      </c>
-      <c r="F471" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G471" t="inlineStr"/>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr"/>
-      <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
-      <c r="M471" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>SPAIN 1</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="F472" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G472" t="inlineStr"/>
-      <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
-      <c r="M472" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>FRANCE 1</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="F473" t="n">
-        <v>23</v>
-      </c>
-      <c r="G473" t="inlineStr"/>
-      <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
-      <c r="M473" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>PARAGUAY 1</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>Deportivo Recoleta</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>Cerro Porteno</t>
-        </is>
-      </c>
-      <c r="F474" t="n">
-        <v>24</v>
-      </c>
-      <c r="G474" t="inlineStr"/>
-      <c r="H474" t="inlineStr"/>
-      <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
-      <c r="M474" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>TURKEY 2</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>76 Igdir Belediyespor</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>Manisa FK</t>
-        </is>
-      </c>
-      <c r="F475" t="n">
-        <v>17</v>
-      </c>
-      <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
-      <c r="M475" t="inlineStr"/>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>Al-Feiha</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>Al-Kholood Club</t>
-        </is>
-      </c>
-      <c r="F476" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
-      <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
-      <c r="M476" t="inlineStr"/>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>FRANCE 1</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="F477" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
-      <c r="J477" t="inlineStr"/>
-      <c r="K477" t="inlineStr"/>
-      <c r="L477" t="inlineStr"/>
-      <c r="M477" t="inlineStr"/>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>VENEZUELA 1</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>Academia Anzoategui FC</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>Monagas</t>
-        </is>
-      </c>
-      <c r="F478" t="n">
-        <v>18</v>
-      </c>
-      <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr"/>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
-      <c r="M478" t="inlineStr"/>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>PARAGUAY 1</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>Deportivo Recoleta</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>Cerro Porteno</t>
-        </is>
-      </c>
-      <c r="F479" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
-      <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
-      <c r="M479" t="inlineStr"/>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>VENEZUELA 1</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>Estudiantes de Merida</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>Universidad de Venezuela</t>
-        </is>
-      </c>
-      <c r="F480" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
-      <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
-      <c r="M480" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M409"/>
+  <dimension ref="A1:M401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16176,31 +16176,31 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>DENMARK 2</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
@@ -16213,31 +16213,31 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Fc Kharkiv</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Obolon-Brovar Kiev</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
@@ -16250,31 +16250,31 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -16287,31 +16287,31 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Lay 0x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>NORWAY 2</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
@@ -16324,31 +16324,31 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ARGENTINA CUP</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -16361,12 +16361,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16376,16 +16376,16 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -16398,31 +16398,31 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Comerciantes Unidos</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -16482,21 +16482,21 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Charlton</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
@@ -16519,21 +16519,21 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="F370" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
@@ -16588,26 +16588,26 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
@@ -16667,21 +16667,21 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Stoke</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Charlton</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
@@ -16704,21 +16704,21 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="F374" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
@@ -16741,21 +16741,21 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
@@ -16768,31 +16768,31 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
@@ -16810,26 +16810,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Lay 2x2</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
@@ -16842,31 +16842,31 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
@@ -16879,7 +16879,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -16889,21 +16889,21 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
@@ -16916,7 +16916,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -16926,21 +16926,21 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
@@ -16953,31 +16953,31 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>ENGLAND 3</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
@@ -16990,7 +16990,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -17000,21 +17000,21 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
@@ -17027,7 +17027,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -17037,21 +17037,21 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -17074,17 +17074,17 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F384" t="n">
@@ -17101,31 +17101,31 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
@@ -17138,31 +17138,31 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
@@ -17175,31 +17175,31 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
@@ -17212,31 +17212,31 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
@@ -17249,7 +17249,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -17259,21 +17259,21 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
@@ -17286,31 +17286,31 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
@@ -17323,31 +17323,31 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
@@ -17360,31 +17360,31 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
@@ -17397,31 +17397,31 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
@@ -17434,31 +17434,31 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
@@ -17471,31 +17471,31 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
@@ -17508,31 +17508,31 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
@@ -17545,31 +17545,31 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Blackburn</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Sheff Utd</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
@@ -17582,31 +17582,31 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
@@ -17619,31 +17619,31 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
@@ -17656,31 +17656,31 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
@@ -17693,31 +17693,31 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Lay 0x3</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
@@ -17727,302 +17727,6 @@
       <c r="L401" t="inlineStr"/>
       <c r="M401" t="inlineStr"/>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>Al-Adalh</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>Al-Saqer FC</t>
-        </is>
-      </c>
-      <c r="F402" t="n">
-        <v>18</v>
-      </c>
-      <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr"/>
-      <c r="M402" t="inlineStr"/>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>Al Jabalain</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>Al-Wahda (KSA)</t>
-        </is>
-      </c>
-      <c r="F403" t="n">
-        <v>18</v>
-      </c>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
-      <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
-      <c r="M403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>TURKEY 1</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>Rizespor</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>Alanyaspor</t>
-        </is>
-      </c>
-      <c r="F404" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
-      <c r="M404" t="inlineStr"/>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>ITALY 2</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>Sampdoria</t>
-        </is>
-      </c>
-      <c r="F405" t="n">
-        <v>20</v>
-      </c>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
-      <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
-      <c r="L405" t="inlineStr"/>
-      <c r="M405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>SPAIN 2</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>Sabadell</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>Cordoba</t>
-        </is>
-      </c>
-      <c r="F406" t="n">
-        <v>19</v>
-      </c>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
-      <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr"/>
-      <c r="M406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="F407" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
-      <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr"/>
-      <c r="M407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>ITALY 1</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="F408" t="n">
-        <v>20</v>
-      </c>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr"/>
-      <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr"/>
-      <c r="L408" t="inlineStr"/>
-      <c r="M408" t="inlineStr"/>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>BRAZIL 1</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>EC Vitoria Salvador</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>Gremio</t>
-        </is>
-      </c>
-      <c r="F409" t="n">
-        <v>20</v>
-      </c>
-      <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
-      <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
-      <c r="L409" t="inlineStr"/>
-      <c r="M409" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/placares_manuais.xlsx
+++ b/placares_manuais.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M401"/>
+  <dimension ref="A1:M392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16176,7 +16176,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16186,21 +16186,21 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>DENMARK 2</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fc Kharkiv</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Obolon-Brovar Kiev</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
@@ -16223,21 +16223,21 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Fc Kharkiv</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Obolon-Brovar Kiev</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
@@ -16260,21 +16260,21 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>NORWAY 2</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
@@ -16297,21 +16297,21 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>NORWAY 2</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr"/>
@@ -16334,21 +16334,21 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
@@ -16371,21 +16371,21 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Comerciantes Unidos</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -16398,31 +16398,31 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lay Draw</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
@@ -16435,31 +16435,31 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
@@ -16472,31 +16472,31 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay Draw</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
@@ -16884,26 +16884,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 0x1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
@@ -16921,26 +16921,26 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Lay 0x0</t>
+          <t>Lay 1x0</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
@@ -16953,31 +16953,31 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Lay 0x1</t>
+          <t>Lay 0x0</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
@@ -16990,7 +16990,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F382" t="n">
@@ -17027,7 +17027,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -17037,21 +17037,21 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -17074,21 +17074,21 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>EUROPA CHAMPIONS LEAGUE</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Slavia Prague</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
@@ -17101,7 +17101,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -17111,21 +17111,21 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
@@ -17138,7 +17138,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -17148,21 +17148,21 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
@@ -17175,31 +17175,31 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
@@ -17212,12 +17212,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17227,16 +17227,16 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
@@ -17249,12 +17249,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lay 1x0</t>
+          <t>Lay 2x0</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17264,16 +17264,16 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
@@ -17286,31 +17286,31 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x2</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ENGLAND 3</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
@@ -17323,31 +17323,31 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 0x3</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
@@ -17360,31 +17360,31 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Lay 2x0</t>
+          <t>Lay 2x2</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SERBIA 2</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>FK Teleoptik Zemun</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>FK Proleter Zrenjanin</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
@@ -17394,339 +17394,6 @@
       <c r="L392" t="inlineStr"/>
       <c r="M392" t="inlineStr"/>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Lay 2x0</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>BRAZIL 2</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="F393" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
-      <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr"/>
-      <c r="L393" t="inlineStr"/>
-      <c r="M393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>Dhamk</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>Al-Ula FC</t>
-        </is>
-      </c>
-      <c r="F394" t="n">
-        <v>26</v>
-      </c>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
-      <c r="M394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>SAUDI ARABIA 1</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>Al-Hazm (KSA)</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>Al-Taawoun Buraidah</t>
-        </is>
-      </c>
-      <c r="F395" t="n">
-        <v>26</v>
-      </c>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr"/>
-      <c r="L395" t="inlineStr"/>
-      <c r="M395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>ENGLAND CUP</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>Leyton Orient</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>Bradford</t>
-        </is>
-      </c>
-      <c r="F396" t="n">
-        <v>34</v>
-      </c>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr"/>
-      <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
-      <c r="M396" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Lay 0x3</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>ENGLAND 2</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>Blackburn</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>Sheff Utd</t>
-        </is>
-      </c>
-      <c r="F397" t="n">
-        <v>34</v>
-      </c>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>FINLAND 1</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>VPS</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>AC Oulu</t>
-        </is>
-      </c>
-      <c r="F398" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
-      <c r="M398" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>ENGLAND CUP</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>Leyton Orient</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>Bradford</t>
-        </is>
-      </c>
-      <c r="F399" t="n">
-        <v>18</v>
-      </c>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
-      <c r="M399" t="inlineStr"/>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>ENGLAND 2</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>Preston</t>
-        </is>
-      </c>
-      <c r="F400" t="n">
-        <v>17</v>
-      </c>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
-      <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr"/>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Lay 2x2</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>ENGLAND 2</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="F401" t="n">
-        <v>17</v>
-      </c>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
-      <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
